--- a/연구코드/results/regression/sinchon/all/regression_results.xlsx
+++ b/연구코드/results/regression/sinchon/all/regression_results.xlsx
@@ -557,13 +557,13 @@
         <v>0.0333</v>
       </c>
       <c r="M2">
-        <v>0.7999000000000001</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="N2">
-        <v>0.5256</v>
+        <v>0.8983</v>
       </c>
       <c r="O2">
-        <v>0.8901</v>
+        <v>0.7246</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -604,13 +604,13 @@
         <v>0.0347</v>
       </c>
       <c r="M3">
-        <v>0.7983</v>
+        <v>0.7841</v>
       </c>
       <c r="N3">
-        <v>0.5351</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="O3">
-        <v>0.8848</v>
+        <v>0.7508</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -651,13 +651,13 @@
         <v>0.0398</v>
       </c>
       <c r="M4">
-        <v>0.8046</v>
+        <v>0.7675</v>
       </c>
       <c r="N4">
-        <v>0.5413</v>
+        <v>0.9015</v>
       </c>
       <c r="O4">
-        <v>0.8911</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -698,13 +698,13 @@
         <v>0.0328</v>
       </c>
       <c r="M5">
-        <v>0.7943</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="N5">
-        <v>0.5382</v>
+        <v>0.876</v>
       </c>
       <c r="O5">
-        <v>0.8784999999999999</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -745,13 +745,13 @@
         <v>0.0357</v>
       </c>
       <c r="M6">
-        <v>0.7943</v>
+        <v>0.7833</v>
       </c>
       <c r="N6">
-        <v>0.5414</v>
+        <v>0.9014</v>
       </c>
       <c r="O6">
-        <v>0.8774999999999999</v>
+        <v>0.7445000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/regression/sinchon/all/regression_results.xlsx
+++ b/연구코드/results/regression/sinchon/all/regression_results.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>Hospital</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Case 5 +AEC_new +Scanner</t>
+  </si>
+  <si>
+    <t>F:95.0/M:131.0</t>
   </si>
   <si>
     <t>Case1_Clinical</t>
@@ -547,23 +550,23 @@
       <c r="I2">
         <v>18.42</v>
       </c>
-      <c r="J2">
-        <v>103</v>
+      <c r="J2" t="s">
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>0.8577</v>
+        <v>0.7513</v>
       </c>
       <c r="L2">
-        <v>0.0333</v>
+        <v>0.0332</v>
       </c>
       <c r="M2">
-        <v>0.7675999999999999</v>
+        <v>0.6541</v>
       </c>
       <c r="N2">
-        <v>0.8983</v>
+        <v>0.7988</v>
       </c>
       <c r="O2">
-        <v>0.7246</v>
+        <v>0.6073</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -594,23 +597,23 @@
       <c r="I3">
         <v>18.37</v>
       </c>
-      <c r="J3">
-        <v>103</v>
+      <c r="J3" t="s">
+        <v>22</v>
       </c>
       <c r="K3">
-        <v>0.8587</v>
+        <v>0.7502</v>
       </c>
       <c r="L3">
-        <v>0.0347</v>
+        <v>0.0362</v>
       </c>
       <c r="M3">
-        <v>0.7841</v>
+        <v>0.6596</v>
       </c>
       <c r="N3">
-        <v>0.8856000000000001</v>
+        <v>0.8055</v>
       </c>
       <c r="O3">
-        <v>0.7508</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -641,23 +644,23 @@
       <c r="I4">
         <v>18.48</v>
       </c>
-      <c r="J4">
-        <v>103</v>
+      <c r="J4" t="s">
+        <v>22</v>
       </c>
       <c r="K4">
-        <v>0.8532999999999999</v>
+        <v>0.7492</v>
       </c>
       <c r="L4">
-        <v>0.0398</v>
+        <v>0.0239</v>
       </c>
       <c r="M4">
-        <v>0.7675</v>
+        <v>0.6762</v>
       </c>
       <c r="N4">
-        <v>0.9015</v>
+        <v>0.7857</v>
       </c>
       <c r="O4">
-        <v>0.7236</v>
+        <v>0.6405999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -688,23 +691,23 @@
       <c r="I5">
         <v>18.56</v>
       </c>
-      <c r="J5">
-        <v>103</v>
+      <c r="J5" t="s">
+        <v>22</v>
       </c>
       <c r="K5">
-        <v>0.8579</v>
+        <v>0.7529</v>
       </c>
       <c r="L5">
-        <v>0.0328</v>
+        <v>0.0321</v>
       </c>
       <c r="M5">
-        <v>0.7927999999999999</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="N5">
-        <v>0.876</v>
+        <v>0.7572</v>
       </c>
       <c r="O5">
-        <v>0.7654</v>
+        <v>0.6896</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -735,23 +738,23 @@
       <c r="I6">
         <v>18.48</v>
       </c>
-      <c r="J6">
-        <v>103</v>
+      <c r="J6" t="s">
+        <v>22</v>
       </c>
       <c r="K6">
-        <v>0.8531</v>
+        <v>0.7493</v>
       </c>
       <c r="L6">
-        <v>0.0357</v>
+        <v>0.0342</v>
       </c>
       <c r="M6">
-        <v>0.7833</v>
+        <v>0.7164</v>
       </c>
       <c r="N6">
-        <v>0.9014</v>
+        <v>0.6987</v>
       </c>
       <c r="O6">
-        <v>0.7445000000000001</v>
+        <v>0.7219</v>
       </c>
     </row>
   </sheetData>
@@ -766,47 +769,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>0.5646485717864669</v>
       </c>
       <c r="C2">
-        <v>0.564693079182782</v>
+        <v>0.5646930791827818</v>
       </c>
       <c r="D2">
-        <v>0.5525728319336562</v>
+        <v>0.5525728319336565</v>
       </c>
       <c r="E2">
-        <v>0.5420970433992833</v>
+        <v>0.5420970433992837</v>
       </c>
       <c r="F2">
-        <v>0.5686645829952226</v>
+        <v>0.5686645829952223</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>0.702833950028682</v>
+        <v>0.7028339500286821</v>
       </c>
       <c r="C3">
         <v>0.7022592335770643</v>
@@ -818,18 +821,18 @@
         <v>0.6972186337684237</v>
       </c>
       <c r="F3">
-        <v>0.7002390372938447</v>
+        <v>0.7002390372938445</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0.725515688236422</v>
       </c>
       <c r="C4">
-        <v>0.7248651613990836</v>
+        <v>0.7248651613990837</v>
       </c>
       <c r="D4">
         <v>0.7263340405788257</v>
@@ -843,7 +846,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0.610377823668161</v>
@@ -863,22 +866,22 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>0.5956803954786014</v>
+        <v>0.5956803954786013</v>
       </c>
       <c r="C6">
         <v>0.6008075563668265</v>
       </c>
       <c r="D6">
-        <v>0.5869928930987696</v>
+        <v>0.5869928930987697</v>
       </c>
       <c r="E6">
-        <v>0.6139376357432221</v>
+        <v>0.6139376357432224</v>
       </c>
       <c r="F6">
-        <v>0.6050568319775639</v>
+        <v>0.605056831977564</v>
       </c>
     </row>
   </sheetData>
@@ -893,119 +896,119 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2">
-        <v>0.8504944735311227</v>
+        <v>0.7350470430107526</v>
       </c>
       <c r="C2">
-        <v>0.8370314967173607</v>
+        <v>0.7418514784946236</v>
       </c>
       <c r="D2">
-        <v>0.8312972658522396</v>
+        <v>0.7250504032258065</v>
       </c>
       <c r="E2">
-        <v>0.8384442782348541</v>
+        <v>0.7435315860215054</v>
       </c>
       <c r="F2">
-        <v>0.8276406548657858</v>
+        <v>0.7225302419354839</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>0.8920468711044627</v>
+        <v>0.755880376344086</v>
       </c>
       <c r="C3">
-        <v>0.8970331588132635</v>
+        <v>0.7389112903225806</v>
       </c>
       <c r="D3">
-        <v>0.8937089670073963</v>
+        <v>0.7447076612903226</v>
       </c>
       <c r="E3">
-        <v>0.8904678799966759</v>
+        <v>0.7290826612903225</v>
       </c>
       <c r="F3">
-        <v>0.893044128646223</v>
+        <v>0.7221102150537634</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
-        <v>0.8460899193883488</v>
+        <v>0.7200940860215054</v>
       </c>
       <c r="C4">
-        <v>0.8504113687359761</v>
+        <v>0.7274025537634409</v>
       </c>
       <c r="D4">
-        <v>0.8465885481592287</v>
+        <v>0.7415994623655914</v>
       </c>
       <c r="E4">
-        <v>0.8357849247901603</v>
+        <v>0.7212701612903225</v>
       </c>
       <c r="F4">
-        <v>0.8411867364746946</v>
+        <v>0.7266465053763441</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>0.8048283885980221</v>
+        <v>0.8135920698924731</v>
       </c>
       <c r="C5">
-        <v>0.8098562287043962</v>
+        <v>0.8210685483870969</v>
       </c>
       <c r="D5">
-        <v>0.7942325272168204</v>
+        <v>0.7951108870967742</v>
       </c>
       <c r="E5">
-        <v>0.8211584808443447</v>
+        <v>0.8118279569892473</v>
       </c>
       <c r="F5">
-        <v>0.8072799800548491</v>
+        <v>0.8091397849462366</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>0.8950346225299781</v>
+        <v>0.7316427595628415</v>
       </c>
       <c r="C6">
-        <v>0.8990035466981929</v>
+        <v>0.7218237704918032</v>
       </c>
       <c r="D6">
-        <v>0.9007768957946293</v>
+        <v>0.7397540983606558</v>
       </c>
       <c r="E6">
-        <v>0.9037324776220232</v>
+        <v>0.7588797814207651</v>
       </c>
       <c r="F6">
-        <v>0.8963857456510724</v>
+        <v>0.7663080601092896</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/regression/sinchon/all/regression_results.xlsx
+++ b/연구코드/results/regression/sinchon/all/regression_results.xlsx
@@ -792,16 +792,16 @@
         <v>0.5646485717864669</v>
       </c>
       <c r="C2">
-        <v>0.5646930791827818</v>
+        <v>0.564693079182782</v>
       </c>
       <c r="D2">
-        <v>0.5525728319336565</v>
+        <v>0.5525728319336562</v>
       </c>
       <c r="E2">
-        <v>0.5420970433992837</v>
+        <v>0.5420970433992833</v>
       </c>
       <c r="F2">
-        <v>0.5686645829952223</v>
+        <v>0.5686645829952226</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -809,7 +809,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>0.7028339500286821</v>
+        <v>0.702833950028682</v>
       </c>
       <c r="C3">
         <v>0.7022592335770643</v>
@@ -821,7 +821,7 @@
         <v>0.6972186337684237</v>
       </c>
       <c r="F3">
-        <v>0.7002390372938445</v>
+        <v>0.7002390372938447</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -832,7 +832,7 @@
         <v>0.725515688236422</v>
       </c>
       <c r="C4">
-        <v>0.7248651613990837</v>
+        <v>0.7248651613990836</v>
       </c>
       <c r="D4">
         <v>0.7263340405788257</v>
@@ -869,19 +869,19 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>0.5956803954786013</v>
+        <v>0.5956803954786014</v>
       </c>
       <c r="C6">
         <v>0.6008075563668265</v>
       </c>
       <c r="D6">
-        <v>0.5869928930987697</v>
+        <v>0.5869928930987696</v>
       </c>
       <c r="E6">
-        <v>0.6139376357432224</v>
+        <v>0.6139376357432221</v>
       </c>
       <c r="F6">
-        <v>0.605056831977564</v>
+        <v>0.6050568319775639</v>
       </c>
     </row>
   </sheetData>
